--- a/design/tables/ChallengeTopic.xlsx
+++ b/design/tables/ChallengeTopic.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeTopic" sheetId="1" r:id="Rd9e080d064f54f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeTopic" sheetId="1" r:id="R7b0c051e9a5c448a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -301,6 +301,9 @@
       <x:c r="I1" s="1" t="str">
         <x:v>unlockAfter</x:v>
       </x:c>
+      <x:c r="J1" t="str">
+        <x:v>thumbnailKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="str">
@@ -328,6 +331,9 @@
         <x:v>client</x:v>
       </x:c>
       <x:c r="I2" s="1" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
@@ -359,17 +365,41 @@
       <x:c r="I3" s="1" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="J3" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="1" t="str"/>
-      <x:c r="B4" s="1" t="str"/>
-      <x:c r="C4" s="1" t="str"/>
-      <x:c r="D4" s="1" t="str"/>
-      <x:c r="E4" s="1" t="str"/>
-      <x:c r="F4" s="1" t="str"/>
-      <x:c r="G4" s="1" t="str"/>
-      <x:c r="H4" s="1" t="str"/>
-      <x:c r="I4" s="1" t="str"/>
+      <x:c r="A4" s="1" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="str">
+        <x:v>key</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="str">
+        <x:v>levelId</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="str">
+        <x:v>titleKey</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="str">
+        <x:v>ruleKey</x:v>
+      </x:c>
+      <x:c r="G4" s="1" t="str">
+        <x:v>iconKey</x:v>
+      </x:c>
+      <x:c r="H4" s="1" t="str">
+        <x:v>startPerks</x:v>
+      </x:c>
+      <x:c r="I4" s="1" t="str">
+        <x:v>unlockAfter</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>thumbnailKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="3" t="str">
@@ -399,6 +429,9 @@
       <x:c r="I5" s="3" t="str">
         <x:v>unlockAfter</x:v>
       </x:c>
+      <x:c r="J5" t="str">
+        <x:v>thumbnailKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="1" t="n">
@@ -424,6 +457,9 @@
       </x:c>
       <x:c r="H6" s="1" t="str"/>
       <x:c r="I6" s="1" t="str"/>
+      <x:c r="J6" t="str">
+        <x:v>topic_opening</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="1" t="n">
@@ -453,6 +489,9 @@
       <x:c r="I7" s="1" t="str">
         <x:v>opening</x:v>
       </x:c>
+      <x:c r="J7" t="str">
+        <x:v>topic_express</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="1" t="n">
@@ -482,6 +521,9 @@
       <x:c r="I8" s="1" t="str">
         <x:v>express</x:v>
       </x:c>
+      <x:c r="J8" t="str">
+        <x:v>topic_warehouse</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="1" t="n">
@@ -511,6 +553,9 @@
       <x:c r="I9" s="1" t="str">
         <x:v>warehouse</x:v>
       </x:c>
+      <x:c r="J9" t="str">
+        <x:v>topic_coins</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="1" t="n">
@@ -540,6 +585,9 @@
       <x:c r="I10" s="1" t="str">
         <x:v>coins</x:v>
       </x:c>
+      <x:c r="J10" t="str">
+        <x:v>topic_mini</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="1" t="n">
@@ -568,6 +616,9 @@
       </x:c>
       <x:c r="I11" s="1" t="str">
         <x:v>mini</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>topic_midnight</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/ChallengeTopic.xlsx
+++ b/design/tables/ChallengeTopic.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeTopic" sheetId="1" r:id="R7b0c051e9a5c448a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChallengeTopic" sheetId="1" r:id="Rea564b4794f440fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -441,7 +441,7 @@
         <x:v>opening</x:v>
       </x:c>
       <x:c r="C6" s="1" t="n">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D6" s="1" t="n">
         <x:v>1</x:v>
@@ -469,7 +469,7 @@
         <x:v>express</x:v>
       </x:c>
       <x:c r="C7" s="1" t="n">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="1" t="n">
         <x:v>2</x:v>
@@ -501,7 +501,7 @@
         <x:v>warehouse</x:v>
       </x:c>
       <x:c r="C8" s="1" t="n">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="1" t="n">
         <x:v>3</x:v>
@@ -533,7 +533,7 @@
         <x:v>coins</x:v>
       </x:c>
       <x:c r="C9" s="1" t="n">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="1" t="n">
         <x:v>4</x:v>
@@ -565,7 +565,7 @@
         <x:v>mini</x:v>
       </x:c>
       <x:c r="C10" s="1" t="n">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D10" s="1" t="n">
         <x:v>5</x:v>
@@ -597,7 +597,7 @@
         <x:v>midnight</x:v>
       </x:c>
       <x:c r="C11" s="1" t="n">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D11" s="1" t="n">
         <x:v>6</x:v>
@@ -619,6 +619,134 @@
       </x:c>
       <x:c r="J11" t="str">
         <x:v>topic_midnight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="1" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="str">
+        <x:v>freezer</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="str">
+        <x:v>topics.freezer.title</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="str">
+        <x:v>topics.freezer.rule</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="str">
+        <x:v>perk_G06</x:v>
+      </x:c>
+      <x:c r="H12" s="1" t="str">
+        <x:v>G06</x:v>
+      </x:c>
+      <x:c r="I12" s="1" t="str">
+        <x:v>midnight</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>topic_freezer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="1" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="str">
+        <x:v>gifts</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="str">
+        <x:v>topics.gifts.title</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="str">
+        <x:v>topics.gifts.rule</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="str">
+        <x:v>perk_F03</x:v>
+      </x:c>
+      <x:c r="H13" s="1" t="str">
+        <x:v>F03</x:v>
+      </x:c>
+      <x:c r="I13" s="1" t="str">
+        <x:v>freezer</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>topic_gifts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="1" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="str">
+        <x:v>topics.storm.title</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="str">
+        <x:v>topics.storm.rule</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="str">
+        <x:v>perk_F05</x:v>
+      </x:c>
+      <x:c r="H14" s="1" t="str">
+        <x:v>F05</x:v>
+      </x:c>
+      <x:c r="I14" s="1" t="str">
+        <x:v>gifts</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>topic_storm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="str">
+        <x:v>dawn</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="str">
+        <x:v>topics.dawn.title</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="str">
+        <x:v>topics.dawn.rule</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="str">
+        <x:v>perk_G02</x:v>
+      </x:c>
+      <x:c r="H15" s="1" t="str">
+        <x:v>G02</x:v>
+      </x:c>
+      <x:c r="I15" s="1" t="str">
+        <x:v>storm</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>topic_dawn</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
